--- a/Examples/Powder_Raman/Crystal23/results.ref.xlsx
+++ b/Examples/Powder_Raman/Crystal23/results.ref.xlsx
@@ -130,13 +130,13 @@
     <t>Absorption maximum (L/mole/cm)</t>
   </si>
   <si>
-    <t>Raman R_total (Å4/amu)</t>
+    <t>Raman R_total (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_parallel (Å4/amu)</t>
+    <t>Raman R_parallel (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_perp (Å4/amu)</t>
+    <t>Raman R_perp (Å⁴/amu)</t>
   </si>
   <si>
     <t>No</t>
@@ -1142,13 +1142,13 @@
         <v>4.82079701757274E-09</v>
       </c>
       <c r="I26">
-        <v>1.241274982462807E-21</v>
+        <v>3.783089521858803E-22</v>
       </c>
       <c r="J26">
-        <v>7.551401284967292E-22</v>
+        <v>2.301474490352653E-22</v>
       </c>
       <c r="K26">
-        <v>4.861348539660775E-22</v>
+        <v>1.48161503150615E-22</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1174,13 +1174,13 @@
         <v>3.675312751870706E-09</v>
       </c>
       <c r="I27">
-        <v>2.240966751422924E-22</v>
+        <v>6.829895032059143E-23</v>
       </c>
       <c r="J27">
-        <v>1.773252492364288E-22</v>
+        <v>5.404421275101588E-23</v>
       </c>
       <c r="K27">
-        <v>4.677142590586361E-23</v>
+        <v>1.425473756957554E-23</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1206,13 +1206,13 @@
         <v>3.829094361269207E-09</v>
       </c>
       <c r="I28">
-        <v>5.738936654106757E-22</v>
+        <v>1.749081503252905E-22</v>
       </c>
       <c r="J28">
-        <v>5.377056756522339E-22</v>
+        <v>1.638789741309336E-22</v>
       </c>
       <c r="K28">
-        <v>3.618798975844192E-23</v>
+        <v>1.102917619435687E-23</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1238,13 +1238,13 @@
         <v>2.942020344593645E-29</v>
       </c>
       <c r="I29">
-        <v>0.939673376537048</v>
+        <v>0.2863884759599193</v>
       </c>
       <c r="J29">
-        <v>0.5369562151762122</v>
+        <v>0.1636505576950961</v>
       </c>
       <c r="K29">
-        <v>0.4027171613608359</v>
+        <v>0.1227379182648232</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1270,13 +1270,13 @@
         <v>2.935947856429463E-29</v>
       </c>
       <c r="I30">
-        <v>0.9396604250949009</v>
+        <v>0.2863845286907185</v>
       </c>
       <c r="J30">
-        <v>0.5369488143871876</v>
+        <v>0.1636483021233808</v>
       </c>
       <c r="K30">
-        <v>0.4027116107077134</v>
+        <v>0.1227362265673377</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1302,13 +1302,13 @@
         <v>4.583466121177083E-27</v>
       </c>
       <c r="I31">
-        <v>5.789751522085655E-10</v>
+        <v>1.764568578826134E-10</v>
       </c>
       <c r="J31">
-        <v>5.274390897439813E-10</v>
+        <v>1.60749980626391E-10</v>
       </c>
       <c r="K31">
-        <v>5.153606246458421E-11</v>
+        <v>1.570687725622241E-11</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1334,13 +1334,13 @@
         <v>8624.841344536877</v>
       </c>
       <c r="I32">
-        <v>8.898820175261502</v>
+        <v>2.712133398124475</v>
       </c>
       <c r="J32">
-        <v>8.685332506094266</v>
+        <v>2.64706780221033</v>
       </c>
       <c r="K32">
-        <v>0.2134876691672369</v>
+        <v>0.06506559591414567</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -1366,13 +1366,13 @@
         <v>8200.794076277285</v>
       </c>
       <c r="I33">
-        <v>0.1400685718860512</v>
+        <v>0.04268932783874297</v>
       </c>
       <c r="J33">
-        <v>0.08003918394215138</v>
+        <v>0.02439390162435302</v>
       </c>
       <c r="K33">
-        <v>0.0600293879438998</v>
+        <v>0.01829542621438994</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -1398,13 +1398,13 @@
         <v>8200.794076298953</v>
       </c>
       <c r="I34">
-        <v>0.1400808570394537</v>
+        <v>0.04269307204013009</v>
       </c>
       <c r="J34">
-        <v>0.08004620402463589</v>
+        <v>0.02439604116642588</v>
       </c>
       <c r="K34">
-        <v>0.06003465301481782</v>
+        <v>0.01829703087370421</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -1430,13 +1430,13 @@
         <v>1.613392302709951E-27</v>
       </c>
       <c r="I35">
-        <v>5.716939307140731</v>
+        <v>1.742377273006456</v>
       </c>
       <c r="J35">
-        <v>3.266822461401294</v>
+        <v>0.9956441560579453</v>
       </c>
       <c r="K35">
-        <v>2.450116845739436</v>
+        <v>0.7467331169485112</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -1462,13 +1462,13 @@
         <v>8.384030087474491E-27</v>
       </c>
       <c r="I36">
-        <v>5.716915347972326</v>
+        <v>1.742369970863078</v>
       </c>
       <c r="J36">
-        <v>3.266808770270028</v>
+        <v>0.9956399833503691</v>
       </c>
       <c r="K36">
-        <v>2.450106577702297</v>
+        <v>0.7467299875127086</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -1494,13 +1494,13 @@
         <v>2.82186117209747E-27</v>
       </c>
       <c r="I37">
-        <v>7.355413207315283E-09</v>
+        <v>2.241742323552394E-09</v>
       </c>
       <c r="J37">
-        <v>7.053951416040427E-09</v>
+        <v>2.149864459265633E-09</v>
       </c>
       <c r="K37">
-        <v>3.01461791274857E-10</v>
+        <v>9.187786428676124E-11</v>
       </c>
     </row>
   </sheetData>
